--- a/IDP-Bios.xlsx
+++ b/IDP-Bios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malekshafei/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malekshafei/Desktop/Louisville/Racing-IDP-Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{474DF2FA-FC1C-D945-9C90-9F9764F536AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596CB67C-B3B7-B94D-9EC9-6841BCEE721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="8500" windowWidth="21640" windowHeight="8640" xr2:uid="{1AAF5619-2C61-6048-80AB-717488016C8F}"/>
+    <workbookView xWindow="6760" yWindow="1340" windowWidth="21640" windowHeight="11040" xr2:uid="{1AAF5619-2C61-6048-80AB-717488016C8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="126">
   <si>
     <t>Player</t>
   </si>
@@ -398,6 +398,21 @@
   </si>
   <si>
     <t>2023.04.25</t>
+  </si>
+  <si>
+    <t>Makenna Morris</t>
+  </si>
+  <si>
+    <t>RW, LW</t>
+  </si>
+  <si>
+    <t>2025.08.27</t>
+  </si>
+  <si>
+    <t>Germantown, MD</t>
+  </si>
+  <si>
+    <t>2002.04.26</t>
   </si>
 </sst>
 </file>
@@ -773,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02116217-943A-0142-9308-CC9A3ADEFF6B}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -1022,75 +1037,57 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
       </c>
       <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1099,7 +1096,7 @@
         <v>32</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
@@ -1122,34 +1119,34 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
       </c>
       <c r="J8">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
         <v>25</v>
@@ -1172,25 +1169,25 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
         <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H9" t="s">
         <v>59</v>
@@ -1199,7 +1196,7 @@
         <v>32</v>
       </c>
       <c r="J9">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
         <v>25</v>
@@ -1222,25 +1219,25 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
         <v>59</v>
@@ -1249,7 +1246,7 @@
         <v>32</v>
       </c>
       <c r="J10">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K10" t="s">
         <v>25</v>
@@ -1272,19 +1269,19 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
         <v>59</v>
@@ -1299,7 +1296,7 @@
         <v>32</v>
       </c>
       <c r="J11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
         <v>25</v>
@@ -1322,25 +1319,25 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
         <v>59</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
         <v>59</v>
@@ -1349,7 +1346,7 @@
         <v>32</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
@@ -1372,34 +1369,34 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s">
         <v>32</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
@@ -1422,25 +1419,25 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
         <v>84</v>
@@ -1449,7 +1446,7 @@
         <v>32</v>
       </c>
       <c r="J14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
@@ -1472,25 +1469,25 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
         <v>89</v>
-      </c>
-      <c r="G15" t="s">
-        <v>95</v>
       </c>
       <c r="H15" t="s">
         <v>84</v>
@@ -1499,7 +1496,7 @@
         <v>32</v>
       </c>
       <c r="J15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K15" t="s">
         <v>25</v>
@@ -1522,34 +1519,34 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I16" t="s">
         <v>32</v>
       </c>
       <c r="J16">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -1572,34 +1569,34 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
         <v>83</v>
-      </c>
-      <c r="H17" t="s">
-        <v>84</v>
       </c>
       <c r="I17" t="s">
         <v>32</v>
       </c>
       <c r="J17">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K17" t="s">
         <v>25</v>
@@ -1622,34 +1619,34 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
         <v>83</v>
       </c>
-      <c r="G18" t="s">
-        <v>109</v>
-      </c>
       <c r="H18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I18" t="s">
         <v>32</v>
       </c>
       <c r="J18">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K18" t="s">
         <v>25</v>
@@ -1672,25 +1669,25 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
         <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="H19" t="s">
         <v>83</v>
@@ -1699,7 +1696,7 @@
         <v>32</v>
       </c>
       <c r="J19">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="K19" t="s">
         <v>25</v>
@@ -1722,34 +1719,34 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="H20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J20">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -1772,51 +1769,101 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
         <v>84</v>
       </c>
       <c r="I21" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" t="s">
         <v>32</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>19</v>
       </c>
-      <c r="K21" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" t="s">
-        <v>25</v>
-      </c>
-      <c r="N21" t="s">
-        <v>25</v>
-      </c>
-      <c r="O21" t="s">
-        <v>25</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" t="s">
         <v>25</v>
       </c>
     </row>

--- a/IDP-Bios.xlsx
+++ b/IDP-Bios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/malekshafei/Desktop/Louisville/Racing-IDP-Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596CB67C-B3B7-B94D-9EC9-6841BCEE721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6C70EF-87E1-C84E-97F5-8BB93F1F052A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6760" yWindow="1340" windowWidth="21640" windowHeight="11040" xr2:uid="{1AAF5619-2C61-6048-80AB-717488016C8F}"/>
+    <workbookView xWindow="4720" yWindow="5620" windowWidth="21640" windowHeight="16180" xr2:uid="{1AAF5619-2C61-6048-80AB-717488016C8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="131">
   <si>
     <t>Player</t>
   </si>
@@ -413,6 +413,21 @@
   </si>
   <si>
     <t>2002.04.26</t>
+  </si>
+  <si>
+    <t>Katie Scott</t>
+  </si>
+  <si>
+    <t>2007.06.20</t>
+  </si>
+  <si>
+    <t>Fairview, PA</t>
+  </si>
+  <si>
+    <t>5'3</t>
+  </si>
+  <si>
+    <t>2025.08.07</t>
   </si>
 </sst>
 </file>
@@ -788,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02116217-943A-0142-9308-CC9A3ADEFF6B}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -1066,6 +1081,24 @@
       <c r="J6">
         <v>4</v>
       </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O6" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1119,34 +1152,34 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
       </c>
       <c r="J8">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
         <v>25</v>
@@ -1169,34 +1202,34 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
         <v>32</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
         <v>25</v>
@@ -1219,25 +1252,25 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F10" t="s">
         <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
         <v>59</v>
@@ -1246,7 +1279,7 @@
         <v>32</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K10" t="s">
         <v>25</v>
@@ -1269,25 +1302,25 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
         <v>59</v>
@@ -1296,7 +1329,7 @@
         <v>32</v>
       </c>
       <c r="J11">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K11" t="s">
         <v>25</v>
@@ -1319,19 +1352,19 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
         <v>59</v>
@@ -1346,7 +1379,7 @@
         <v>32</v>
       </c>
       <c r="J12">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
@@ -1369,25 +1402,25 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
         <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
         <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
         <v>59</v>
@@ -1396,7 +1429,7 @@
         <v>32</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
@@ -1419,34 +1452,34 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="I14" t="s">
         <v>32</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
@@ -1469,25 +1502,25 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s">
         <v>84</v>
@@ -1496,7 +1529,7 @@
         <v>32</v>
       </c>
       <c r="J15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K15" t="s">
         <v>25</v>
@@ -1519,25 +1552,25 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
         <v>89</v>
-      </c>
-      <c r="G16" t="s">
-        <v>95</v>
       </c>
       <c r="H16" t="s">
         <v>84</v>
@@ -1546,7 +1579,7 @@
         <v>32</v>
       </c>
       <c r="J16">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -1569,34 +1602,34 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
         <v>32</v>
       </c>
       <c r="J17">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="K17" t="s">
         <v>25</v>
@@ -1619,34 +1652,34 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" t="s">
         <v>83</v>
-      </c>
-      <c r="H18" t="s">
-        <v>84</v>
       </c>
       <c r="I18" t="s">
         <v>32</v>
       </c>
       <c r="J18">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K18" t="s">
         <v>25</v>
@@ -1669,34 +1702,34 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
         <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" t="s">
         <v>83</v>
       </c>
-      <c r="G19" t="s">
-        <v>109</v>
-      </c>
       <c r="H19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I19" t="s">
         <v>32</v>
       </c>
       <c r="J19">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="K19" t="s">
         <v>25</v>
@@ -1719,25 +1752,25 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
         <v>83</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="H20" t="s">
         <v>83</v>
@@ -1746,7 +1779,7 @@
         <v>32</v>
       </c>
       <c r="J20">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -1769,34 +1802,34 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I21" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s">
         <v>25</v>
@@ -1819,51 +1852,101 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s">
         <v>84</v>
       </c>
       <c r="I22" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22">
+        <v>6</v>
+      </c>
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" t="s">
         <v>32</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>19</v>
       </c>
-      <c r="K22" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" t="s">
-        <v>25</v>
-      </c>
-      <c r="N22" t="s">
-        <v>25</v>
-      </c>
-      <c r="O22" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="K23" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" t="s">
+        <v>25</v>
+      </c>
+      <c r="O23" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" t="s">
         <v>25</v>
       </c>
     </row>
